--- a/ig/main/CodeSystem-v3-SpecimenType-supplement-fr.xlsx
+++ b/ig/main/CodeSystem-v3-SpecimenType-supplement-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/v3-SpecimenType-supplement-fr</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/days-of-week-supplement-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-24T16:40:38+11:00</t>
+    <t>2026-08-24T16:40:38+11:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-SpecimenType</t>
+    <t>http://hl7.org/fhir/days-of-week</t>
   </si>
   <si>
     <t>Count</t>
@@ -217,6 +217,27 @@
   </si>
   <si>
     <t>URTH</t>
+  </si>
+  <si>
+    <t>mon</t>
+  </si>
+  <si>
+    <t>tue</t>
+  </si>
+  <si>
+    <t>wed</t>
+  </si>
+  <si>
+    <t>thu</t>
+  </si>
+  <si>
+    <t>fri</t>
+  </si>
+  <si>
+    <t>sat</t>
+  </si>
+  <si>
+    <t>sun</t>
   </si>
 </sst>
 </file>
@@ -514,7 +535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -833,6 +854,76 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
     </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/main/CodeSystem-v3-SpecimenType-supplement-fr.xlsx
+++ b/ig/main/CodeSystem-v3-SpecimenType-supplement-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/days-of-week-supplement-fr</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/v3-SpecimenType-supplement-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T16:40:38+11:00</t>
+    <t>2025-10-24T16:40:38+11:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/days-of-week</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-SpecimenType</t>
   </si>
   <si>
     <t>Count</t>
@@ -217,27 +217,6 @@
   </si>
   <si>
     <t>URTH</t>
-  </si>
-  <si>
-    <t>mon</t>
-  </si>
-  <si>
-    <t>tue</t>
-  </si>
-  <si>
-    <t>wed</t>
-  </si>
-  <si>
-    <t>thu</t>
-  </si>
-  <si>
-    <t>fri</t>
-  </si>
-  <si>
-    <t>sat</t>
-  </si>
-  <si>
-    <t>sun</t>
   </si>
 </sst>
 </file>
@@ -535,7 +514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -854,76 +833,6 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
     </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
